--- a/qa-artifacts/FoodHub-AI-Test-Coverage.xlsx
+++ b/qa-artifacts/FoodHub-AI-Test-Coverage.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -542,16 +542,116 @@
         <v>User returns to FoodHub and paid order receipt is shown</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AI-EDGE-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="C8" t="str">
+        <v>FoodHub Web consumer expects stable /menu and /order contracts</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Consumer/provider API contract drift</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Pact verifies GET /menu and POST /order response status, headers, and body shape</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AI-EDGE-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Database</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Paid order persists in a real PostgreSQL database</v>
+      </c>
+      <c r="D9" t="str">
+        <v>API returns success but order is not stored</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Testcontainers starts PostgreSQL and verifies saved order data can be read back</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AI-EDGE-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Load</v>
+      </c>
+      <c r="C10" t="str">
+        <v>API handles repeated browse-and-order traffic</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Performance regression or elevated failure rate under load</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Load</v>
+      </c>
+      <c r="F10" t="str">
+        <v>k6 thresholds pass for p95 latency, HTTP failures, and paid-order failures</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AI-EDGE-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Report</v>
+      </c>
+      <c r="C11" t="str">
+        <v>QA report includes functional, contract, database, and load evidence</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Mandatory add-on evidence missing from review artifacts</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Report</v>
+      </c>
+      <c r="F11" t="str">
+        <v>test-report.html shows Dashboard, Integration Testcontainers case, Contract, E2E, and Load metrics</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>AI-EDGE-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Visual Regression</v>
+      </c>
+      <c r="C12" t="str">
+        <v>UI layout or styling changes unexpectedly</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Checkout UI regressions are missed by functional assertions</v>
+      </c>
+      <c r="E12" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Playwright snapshot assertions compare menu-visible, cart-ready, and gateway-ready baselines</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -655,16 +755,118 @@
         <v>Candidate</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AI-COV-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Consumer/provider contract regression</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Frontend can break if API fields or status codes change</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Use Pact to verify /menu and successful /order expectations</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Implemented</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AI-COV-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Real database persistence</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Mocked persistence can miss PostgreSQL schema or serialization bugs</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Use Testcontainers PostgreSQL to create an order and query it back</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Implemented</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AI-COV-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Load-test endpoint hit accounting</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Reviewers need to know how much traffic was generated per endpoint</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Report k6 VUs, iterations, total requests, and /health, /menu, /order hits</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Implemented</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AI-COV-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Missing cardId in API order request</v>
+      </c>
+      <c r="C10" t="str">
+        <v>cardId is optional in schema but the checkout may rely on selected-card traceability</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Submit a valid paid order without cardId and verify accepted behavior is intentional</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Candidate</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AI-COV-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Testcontainers unavailable in CI</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Real DB tests depend on Docker availability</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Document or gate real DB tests when Docker/Testcontainers cannot start</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Candidate</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>AI-COV-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Visual regression for checkout UI</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Functional E2E tests may pass even if layout, spacing, or visual hierarchy breaks</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Use Playwright screenshot snapshots for menu-visible, cart-ready, gateway-ready, declined-payment, fake-card, and receipt states</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Partially Implemented</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -751,16 +953,84 @@
         <v>Validate totals across repeated menu item ids</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>AI-DATA-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>E2E checkout scenario</v>
+      </c>
+      <c r="C6" t="str">
+        <v>createApprovedCheckout()</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Classic Burger, $9.50, CVV 123</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Keep Playwright happy path data centralized and readable</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AI-DATA-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>E2E declined card</v>
+      </c>
+      <c r="C7" t="str">
+        <v>createDeclinedPaymentCard()</v>
+      </c>
+      <c r="D7" t="str">
+        <v>declined-card with masked number xxxx-xxxx-xxxx-8911</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Keep payment failure browser data isolated per test</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AI-DATA-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>PostgreSQL persisted order</v>
+      </c>
+      <c r="C8" t="str">
+        <v>createOrder([{ menuItemId: 'burger-classic', quantity: 2 }])</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Saved order total 19 with paymentId pay_testcontainers</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Verify real DB persistence and JSONB item serialization</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AI-DATA-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>k6 deterministic traffic accounting</v>
+      </c>
+      <c r="C9" t="str">
+        <v>One k6 iteration calls /health, /menu, and /order once</v>
+      </c>
+      <c r="D9" t="str">
+        <v>218 iterations = 654 total API requests</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Make load-test evidence easy to audit</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -814,12 +1084,23 @@
         <v>Review output</v>
       </c>
       <c r="C5" t="str">
-        <v>Look for timeout, selector, network, environment, retry, and ordering patterns</v>
+        <v>Look for timeout, selector, network, Docker/Testcontainers, Pact verifier, k6 threshold, environment, retry, and ordering patterns</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Feed current project context</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Include contract tests, Testcontainers PostgreSQL persistence, k6 load summary, and Playwright E2E artifacts in the AI prompt</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/qa-artifacts/FoodHub-AI-Test-Coverage.xlsx
+++ b/qa-artifacts/FoodHub-AI-Test-Coverage.xlsx
@@ -3,10 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="AI Edge Cases" sheetId="1" r:id="rId1"/>
-    <sheet name="Coverage Expansion" sheetId="2" r:id="rId2"/>
-    <sheet name="Generated Test Data" sheetId="3" r:id="rId3"/>
-    <sheet name="Failure Analysis" sheetId="4" r:id="rId4"/>
+    <sheet name="Failure Analysis" sheetId="1" r:id="rId1"/>
+    <sheet name="AI Edge Cases" sheetId="2" r:id="rId2"/>
+    <sheet name="Missing Test Scenarios" sheetId="3" r:id="rId3"/>
+    <sheet name="Coverage Expansion" sheetId="4" r:id="rId4"/>
+    <sheet name="Test Data Suggestions" sheetId="5" r:id="rId5"/>
+    <sheet name="Run Configuration" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -400,7 +402,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:K4"/>
+  <cols>
+    <col min="1" max="1" width="17.83203125" customWidth="1"/>
+    <col min="2" max="2" width="33.83203125" customWidth="1"/>
+    <col min="3" max="3" width="64.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="59.83203125" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" customWidth="1"/>
+    <col min="8" max="8" width="64.83203125" customWidth="1"/>
+    <col min="9" max="9" width="64.83203125" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,686 +436,3071 @@
       <c r="F1" t="str">
         <v>Expected_Result</v>
       </c>
+      <c r="G1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Evidence</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Prompt_Source</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Model_Used</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AI-EDGE-001</v>
+        <v>E2E-CONN-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Menu</v>
+        <v>E2E - App Startup / Environment</v>
       </c>
       <c r="C2" t="str">
-        <v>Menu API returns stable item contract</v>
+        <v>Menu and payment flow: connection refused on first navigation</v>
       </c>
       <c r="D2" t="str">
-        <v>API contract breaking</v>
+        <v>Medium</v>
       </c>
       <c r="E2" t="str">
-        <v>Integration</v>
+        <v>E2E</v>
       </c>
       <c r="F2" t="str">
-        <v>GET /menu returns items with id, name, price, and category</v>
+        <v>App loads menu successfully on first attempt</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H2" t="str">
+        <v>page.goto: net::ERR_CONNECTION_REFUSED at http://127.0.0.1:4173/</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Retry passed; flaky due to server readiness. Add a health check wait before navigation or use retries.</v>
+      </c>
+      <c r="J2" t="str">
+        <v>sample-flaky-log.txt</v>
+      </c>
+      <c r="K2" t="str">
+        <v>N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AI-EDGE-002</v>
+        <v>E2E-GATEWAY-001</v>
       </c>
       <c r="B3" t="str">
-        <v>Order</v>
+        <v>E2E - Payment Gateway</v>
       </c>
       <c r="C3" t="str">
-        <v>Order contains an unknown menu item</v>
+        <v>Declined card payment: gateway message not updated in time</v>
       </c>
       <c r="D3" t="str">
-        <v>Invalid menu items</v>
+        <v>Medium</v>
       </c>
       <c r="E3" t="str">
-        <v>Integration</v>
+        <v>E2E</v>
       </c>
       <c r="F3" t="str">
-        <v>POST /order returns 400 Invalid order</v>
+        <v>Gateway shows 'Payment declined for xxxx-xxxx-xxxx-8911.'</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H3" t="str">
+        <v>expect(locator('#gateway-message')).toHaveText: Timeout 5000ms exceeded. Received: 'Processing through FoodHub Payment Gateway...'</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Missing wait for the declined text; page may need longer timeout or a more robust assertion. Could indicate slow gateway response in CI.</v>
+      </c>
+      <c r="J3" t="str">
+        <v>sample-flaky-log.txt</v>
+      </c>
+      <c r="K3" t="str">
+        <v>N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AI-EDGE-003</v>
+        <v>E2E-RETRY-001</v>
       </c>
       <c r="B4" t="str">
-        <v>Order</v>
+        <v>E2E - Test Stability</v>
       </c>
       <c r="C4" t="str">
-        <v>Order contains no items</v>
+        <v>Menu/payment flow flakiness: first attempt connection refused, retry passes</v>
       </c>
       <c r="D4" t="str">
-        <v>Invalid empty orders</v>
+        <v>High</v>
       </c>
       <c r="E4" t="str">
-        <v>Integration</v>
+        <v>E2E</v>
       </c>
       <c r="F4" t="str">
-        <v>POST /order returns 400 with empty-order detail</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>AI-EDGE-004</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Totals</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Order has mixed item quantities and decimal prices</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Incorrect totals</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Unit</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Total is rounded to two decimals and payment is charged once</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>AI-EDGE-005</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Payment</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Gateway returns declined card</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Payment failures</v>
-      </c>
-      <c r="E6" t="str">
-        <v>E2E</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Gateway displays decline and order is not created</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>AI-EDGE-006</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Payment</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Gateway returns approved payment</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Checkout completion</v>
-      </c>
-      <c r="E7" t="str">
-        <v>E2E</v>
-      </c>
-      <c r="F7" t="str">
-        <v>User returns to FoodHub and paid order receipt is shown</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>AI-EDGE-007</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Contract</v>
-      </c>
-      <c r="C8" t="str">
-        <v>FoodHub Web consumer expects stable /menu and /order contracts</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Consumer/provider API contract drift</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Contract</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Pact verifies GET /menu and POST /order response status, headers, and body shape</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>AI-EDGE-008</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Database</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Paid order persists in a real PostgreSQL database</v>
-      </c>
-      <c r="D9" t="str">
-        <v>API returns success but order is not stored</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Integration</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Testcontainers starts PostgreSQL and verifies saved order data can be read back</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>AI-EDGE-009</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Load</v>
-      </c>
-      <c r="C10" t="str">
-        <v>API handles repeated browse-and-order traffic</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Performance regression or elevated failure rate under load</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Load</v>
-      </c>
-      <c r="F10" t="str">
-        <v>k6 thresholds pass for p95 latency, HTTP failures, and paid-order failures</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>AI-EDGE-010</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Report</v>
-      </c>
-      <c r="C11" t="str">
-        <v>QA report includes functional, contract, database, and load evidence</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Mandatory add-on evidence missing from review artifacts</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Report</v>
-      </c>
-      <c r="F11" t="str">
-        <v>test-report.html shows Dashboard, Integration Testcontainers case, Contract, E2E, and Load metrics</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>AI-EDGE-011</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Visual Regression</v>
-      </c>
-      <c r="C12" t="str">
-        <v>UI layout or styling changes unexpectedly</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Checkout UI regressions are missed by functional assertions</v>
-      </c>
-      <c r="E12" t="str">
-        <v>E2E</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Playwright snapshot assertions compare menu-visible, cart-ready, and gateway-ready baselines</v>
+        <v>Test passes on first attempt without retries</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="H4" t="str">
+        <v>page.goto: net::ERR_CONNECTION_REFUSED ... Retry #1 ok [chromium] ...</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Flaky test erodes confidence. Add explicit retries or server health check before starting E2E tests to stabilize.</v>
+      </c>
+      <c r="J4" t="str">
+        <v>sample-flaky-log.txt</v>
+      </c>
+      <c r="K4" t="str">
+        <v>N/A</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:K34"/>
+  <cols>
+    <col min="1" max="1" width="13.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="64.83203125" customWidth="1"/>
+    <col min="4" max="4" width="64.83203125" customWidth="1"/>
+    <col min="5" max="5" width="23.83203125" customWidth="1"/>
+    <col min="6" max="6" width="64.83203125" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="64.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>ID</v>
       </c>
       <c r="B1" t="str">
-        <v>AI_Suggested_Scenario</v>
+        <v>Area</v>
       </c>
       <c r="C1" t="str">
-        <v>Why_It_Matters</v>
+        <v>Scenario</v>
       </c>
       <c r="D1" t="str">
-        <v>Proposed_Test</v>
+        <v>Risk</v>
       </c>
       <c r="E1" t="str">
+        <v>Test_Level</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Expected_Result</v>
+      </c>
+      <c r="G1" t="str">
         <v>Status</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Evidence</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Prompt_Source</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Model_Used</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AI-COV-001</v>
+        <v>API-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Duplicate items</v>
+        <v>API</v>
       </c>
       <c r="C2" t="str">
-        <v>Duplicate lines can expose total-calculation mistakes</v>
+        <v>POST /order with empty items array</v>
       </c>
       <c r="D2" t="str">
-        <v>Submit the same menu item twice as separate lines</v>
+        <v>Order created without items leads to incorrect state</v>
       </c>
       <c r="E2" t="str">
-        <v>Implemented</v>
+        <v>Integration</v>
+      </c>
+      <c r="F2" t="str">
+        <v>400 Bad Request with error 'Invalid order' and details 'Order must contain at least one item'</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>Already tested but edge: empty array vs missing items field</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K2" t="str">
+        <v>DeepSeek-R1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AI-COV-002</v>
+        <v>API-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Large orders</v>
+        <v>API</v>
       </c>
       <c r="C3" t="str">
-        <v>Boundary quantities can break validation or totals</v>
+        <v>POST /order with items having quantity &gt;20</v>
       </c>
       <c r="D3" t="str">
-        <v>Submit quantity 20, the maximum accepted value</v>
+        <v>Boundary violation could cause overflow or incorrect total</v>
       </c>
       <c r="E3" t="str">
-        <v>Implemented</v>
+        <v>Integration</v>
+      </c>
+      <c r="F3" t="str">
+        <v>400 Bad Request with details 'Quantity must be an integer between 1 and 20'</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>Boundary value 21</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K3" t="str">
+        <v>DeepSeek-R1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AI-COV-003</v>
+        <v>API-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Invalid payload shapes</v>
+        <v>API</v>
       </c>
       <c r="C4" t="str">
-        <v>Malformed clients should receive predictable errors</v>
+        <v>POST /order with quantity as floating point (2.5)</v>
       </c>
       <c r="D4" t="str">
-        <v>Submit items as an object instead of an array</v>
+        <v>Type coercion or logic error</v>
       </c>
       <c r="E4" t="str">
-        <v>Implemented</v>
+        <v>Integration</v>
+      </c>
+      <c r="F4" t="str">
+        <v>400 Bad Request (ZodError) because quantity must be integer</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Zod schema requires int().positive(); should reject float</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K4" t="str">
+        <v>DeepSeek-R1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AI-COV-004</v>
+        <v>API-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Missing payment token</v>
+        <v>API</v>
       </c>
       <c r="C5" t="str">
-        <v>Orders must not bypass gateway payment</v>
+        <v>POST /order with quantity negative (-1)</v>
       </c>
       <c r="D5" t="str">
-        <v>Submit otherwise valid order without paymentToken</v>
+        <v>Negative quantity pass validation?</v>
       </c>
       <c r="E5" t="str">
-        <v>Candidate</v>
+        <v>Integration</v>
+      </c>
+      <c r="F5" t="str">
+        <v>400 Bad Request because positive constraint</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Zod positive() rejects zero? Check: positive() means &gt;0, so -1 rejected</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K5" t="str">
+        <v>DeepSeek-R1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AI-COV-005</v>
+        <v>API-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Gateway cancellation</v>
+        <v>API</v>
       </c>
       <c r="C6" t="str">
-        <v>Cancelled payments must not create orders</v>
+        <v>POST /order with quantity zero</v>
       </c>
       <c r="D6" t="str">
-        <v>Click cancel on FoodHub Payment Gateway</v>
+        <v>Edge case: zero quantity might be allowed but lineTotal zero</v>
       </c>
       <c r="E6" t="str">
-        <v>Candidate</v>
+        <v>Integration</v>
+      </c>
+      <c r="F6" t="str">
+        <v>400 Bad Request (ZodError) because positive() excludes 0</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Zod positive() rejects 0; service also checks quantity &lt; 1</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K6" t="str">
+        <v>DeepSeek-R1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>AI-COV-006</v>
+        <v>API-006</v>
       </c>
       <c r="B7" t="str">
-        <v>Consumer/provider contract regression</v>
+        <v>API</v>
       </c>
       <c r="C7" t="str">
-        <v>Frontend can break if API fields or status codes change</v>
+        <v>POST /order with missing paymentToken</v>
       </c>
       <c r="D7" t="str">
-        <v>Use Pact to verify /menu and successful /order expectations</v>
+        <v>Missing required field leads to 500 or payment bypass</v>
       </c>
       <c r="E7" t="str">
-        <v>Implemented</v>
+        <v>Integration</v>
+      </c>
+      <c r="F7" t="str">
+        <v>400 Bad Request (ZodError) because paymentToken is required min 1</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Zod schema requires min(1) so missing field triggers error</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K7" t="str">
+        <v>DeepSeek-R1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>AI-COV-007</v>
+        <v>API-007</v>
       </c>
       <c r="B8" t="str">
-        <v>Real database persistence</v>
+        <v>API</v>
       </c>
       <c r="C8" t="str">
-        <v>Mocked persistence can miss PostgreSQL schema or serialization bugs</v>
+        <v>POST /order with invalid paymentToken (not starting with gateway_paid_ or tok_success)</v>
       </c>
       <c r="D8" t="str">
-        <v>Use Testcontainers PostgreSQL to create an order and query it back</v>
+        <v>Payment might be processed incorrectly</v>
       </c>
       <c r="E8" t="str">
-        <v>Implemented</v>
+        <v>Integration</v>
+      </c>
+      <c r="F8" t="str">
+        <v>402 Payment Failed with reason 'Payment was not completed through FoodHub Payment Gateway'</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>FakePaymentGateway rejects tokens not matching pattern</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K8" t="str">
+        <v>DeepSeek-R1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>AI-COV-008</v>
+        <v>API-008</v>
       </c>
       <c r="B9" t="str">
-        <v>Load-test endpoint hit accounting</v>
+        <v>API</v>
       </c>
       <c r="C9" t="str">
-        <v>Reviewers need to know how much traffic was generated per endpoint</v>
+        <v>POST /order with paymentToken 'tok_fail'</v>
       </c>
       <c r="D9" t="str">
-        <v>Report k6 VUs, iterations, total requests, and /health, /menu, /order hits</v>
+        <v>Declined payment should fail gracefully</v>
       </c>
       <c r="E9" t="str">
-        <v>Implemented</v>
+        <v>Integration</v>
+      </c>
+      <c r="F9" t="str">
+        <v>402 Payment Failed with reason 'Payment authorization failed'</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Similar to gateway_declined_* pattern</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K9" t="str">
+        <v>DeepSeek-R1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>AI-COV-009</v>
+        <v>API-009</v>
       </c>
       <c r="B10" t="str">
-        <v>Missing cardId in API order request</v>
+        <v>API</v>
       </c>
       <c r="C10" t="str">
-        <v>cardId is optional in schema but the checkout may rely on selected-card traceability</v>
+        <v>POST /order with amount $0.00 after validation (e.g., all items free? but menu has no free items)</v>
       </c>
       <c r="D10" t="str">
-        <v>Submit a valid paid order without cardId and verify accepted behavior is intentional</v>
+        <v>Zero total order might be processed</v>
       </c>
       <c r="E10" t="str">
-        <v>Candidate</v>
+        <v>Integration</v>
+      </c>
+      <c r="F10" t="str">
+        <v>400? Payment gateway returns failed because amount &lt;= 0. Service throws OrderValidationError if no items? Actually check: FakePaymentGateway returns failed if amount &lt;= 0. So order creation will throw PaymentFailedError -&gt; 402</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>If all items have price 0? Not possible currently. But edge: could be 0 total due to rounding?</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K10" t="str">
+        <v>DeepSeek-R1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>AI-COV-010</v>
+        <v>API-010</v>
       </c>
       <c r="B11" t="str">
-        <v>Testcontainers unavailable in CI</v>
+        <v>API</v>
       </c>
       <c r="C11" t="str">
-        <v>Real DB tests depend on Docker availability</v>
+        <v>POST /order with null customerName</v>
       </c>
       <c r="D11" t="str">
-        <v>Document or gate real DB tests when Docker/Testcontainers cannot start</v>
+        <v>Null name could cause crash in receipt</v>
       </c>
       <c r="E11" t="str">
-        <v>Candidate</v>
+        <v>Integration</v>
+      </c>
+      <c r="F11" t="str">
+        <v>400 Bad Request (ZodError) because customerName trim min 1</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>Zod schema: z.string().trim().min(1) so null or empty fails</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K11" t="str">
+        <v>DeepSeek-R1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>AI-COV-011</v>
+        <v>API-011</v>
       </c>
       <c r="B12" t="str">
-        <v>Visual regression for checkout UI</v>
+        <v>API</v>
       </c>
       <c r="C12" t="str">
-        <v>Functional E2E tests may pass even if layout, spacing, or visual hierarchy breaks</v>
+        <v>POST /order with customerName containing HTML/JS injection characters</v>
       </c>
       <c r="D12" t="str">
-        <v>Use Playwright screenshot snapshots for menu-visible, cart-ready, gateway-ready, declined-payment, fake-card, and receipt states</v>
+        <v>XSS or rendering issues in UI</v>
       </c>
       <c r="E12" t="str">
-        <v>Partially Implemented</v>
+        <v>Integration</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Order created successfully, name stored as-is</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>No sanitization in API; frontend renders via textContent but invoice shows raw; test for encoding</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K12" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>API-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>API</v>
+      </c>
+      <c r="C13" t="str">
+        <v>POST /order with duplicate item lines (same menuItemId multiple times) – total calculated correctly</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Duplicate lines may double-count or cause logic error</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Order created with two separate lines (same item) and aggregated total</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Already tested in integration test 'handles duplicate item lines', but check with different quantities</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K13" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>UI-001</v>
+      </c>
+      <c r="B14" t="str">
+        <v>UI</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Rapid multiple clicks on Add button for same item</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Race condition, cart may add more than intended</v>
+      </c>
+      <c r="E14" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Cart increments by exactly number of clicks</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>Use Playwright to simulate rapid clicks; verify cart state</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K14" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>UI-002</v>
+      </c>
+      <c r="B15" t="str">
+        <v>UI</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Double-click Checkout button before gateway redirect</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Multiple orders created</v>
+      </c>
+      <c r="E15" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Only one pending order stored; gateway launches once</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>Check sessionStorage for duplicate; app uses sessionStorage set before redirect, subsequent click overwrites? Might cause multiple redirects</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K15" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>UI-003</v>
+      </c>
+      <c r="B16" t="str">
+        <v>UI</v>
+      </c>
+      <c r="C16" t="str">
+        <v>User navigates back after payment gateway redirects to app</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Order state confusion, invoice may show again or error</v>
+      </c>
+      <c r="E16" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Page should handle back navigation gracefully (no duplicate order creation)</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>SessionStorage cleared after order creation; back button might show stale state</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K16" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>UI-004</v>
+      </c>
+      <c r="B17" t="str">
+        <v>UI</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Enter CVV with non-numeric characters (e.g., 'ABC')</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Gateway may accept or reject unexpectedly</v>
+      </c>
+      <c r="E17" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Gateway likely rejects or returns error message; CVV field may have input validation</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>Gateway page has &lt;input type="text"&gt; for CVV? Need to check; assume no validation</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K17" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>UI-005</v>
+      </c>
+      <c r="B18" t="str">
+        <v>UI</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Add fake payment card with exactly 12 digits (boundary)</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Submission validation may fail for minimum digits</v>
+      </c>
+      <c r="E18" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Card saved successfully as digits &gt;= 12</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>Frontend JS checks digits.length &lt; 12, so 12 passes</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K18" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>UI-006</v>
+      </c>
+      <c r="B19" t="str">
+        <v>UI</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Add fake payment card with 19 digits (max typical card length)</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Long input might overflow or be truncated</v>
+      </c>
+      <c r="E19" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Card saved, last four correct</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>No explicit max length</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K19" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Pmt-001</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Payment</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Payment gateway returns success but app server crashes before order creation</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Customer charged but order not created (dual-write inconsistency)</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Component/Integration</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Order should be in 'pending' state and recoverable; currently no recovery mechanism</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>App does not have idempotency or retry; potential data loss</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K20" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Pmt-002</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Payment</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Gateway redirects with paymentId but gatewayStatus missing</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Order creation skips payment step?</v>
+      </c>
+      <c r="E21" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="F21" t="str">
+        <v>App shows error: 'No pending order found' or gatewayStatus check fails</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>UI code checks if gatewayStatus exists; if missing, no action</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K21" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Pmt-003</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Payment</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Gateway timeout (no response) during checkout</v>
+      </c>
+      <c r="D22" t="str">
+        <v>UI may hang or show loading indefinitely</v>
+      </c>
+      <c r="E22" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="F22" t="str">
+        <v>User should see error message after timeout or return to app with failure</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>Gateway is fake, but network delay simulation could be tested</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K22" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Inv-001</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Invoice</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Invoice preview after page refresh using invoice link</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Invoice data lost on page reload because state.lastInvoice is in-memory only</v>
+      </c>
+      <c r="E23" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Invoice link disappears; no persistence</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>Invoice is not stored in localStorage; refresh resets state</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K23" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Inv-002</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Invoice</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Invoice with very long customerName (e.g., 500 characters)</v>
+      </c>
+      <c r="D24" t="str">
+        <v>UI layout breakage</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Visual/E2E</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Name truncated or wrapped but no overflow</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>May need CSS overflow handling</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K24" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Obs-001</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Observability</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Request without x-request-id header</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Missing correlation ID</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Middleware generates a UUID and sets response header</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>Code uses randomUUID() if header absent</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K25" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Obs-002</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Observability</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Concurrent requests with same x-request-id (duplicate)</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Log entries collide</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Both logged with same ID; no functional impact</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>System does not enforce uniqueness</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K26" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Ctr-001</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="C27" t="str">
+        <v>GET /menu response missing optional field (e.g., description)</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Frontend may break if expecting field</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Consumer (Pact) test fails if provider changes schema</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>Contract tests in place but should include field schemas</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K27" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Ctr-002</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="C28" t="str">
+        <v>POST /order response has new field not in consumer expectations</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Consumer not updated, may pass silently</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Pact verification should flag unexpected keys</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>Pact allows Provider to have extra fields unless strict matching is used</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K28" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Persist-001</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Persistence</v>
+      </c>
+      <c r="C29" t="str">
+        <v>OrderRepository.save throws database error after payment succeeds</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Payment charged but order not persisted</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="F29" t="str">
+        <v>OrderService should roll back or log and return 500; currently throws unhandled error -&gt; 500</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>No transaction wrapper; payment already completed</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Code Analysis</v>
+      </c>
+      <c r="K29" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Persist-002</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Persistence</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Two identical orders submitted concurrently</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Duplicate orders with same content</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Load/Integration</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Both succeed, no deduplication; could lead to double charge</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>No idempotency key</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K30" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Vis-001</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Visual</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Checkout page on mobile viewport (375x667)</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Layout broken, buttons overlapping</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Visual E2E</v>
+      </c>
+      <c r="F31" t="str">
+        <v>All elements visible, no horizontal scroll, responsive</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>Playwright with iPhone viewport</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K31" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Vis-002</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Visual</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Long menu list with many items (e.g., 50 items)</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Page performance, scroll issues</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Visual/Load</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Page renders within acceptable time (&lt;2s)</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>Currently only 4 items; test with expanded menu</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K32" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Load-001</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Load</v>
+      </c>
+      <c r="C33" t="str">
+        <v>50 concurrent VUs browsing menu and creating orders</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Performance degradation, order failures rate &gt;2%</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Load</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Thresholds: failure rate &lt;0.05, p95 &lt;500ms, order failures &lt;0.02</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v>k6 load test with 50 VU, steady state 1 min</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K33" t="str">
+        <v>DeepSeek-R1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Load-002</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Load</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Payment gateway becomes slow (500ms delay per request)</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Order creation time increases, timeout</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Load</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Order creation p95 may exceed threshold; order failures may increase if gateway timeout</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Not Run</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v>Simulate gateway latency; observe thresholds</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K34" t="str">
+        <v>DeepSeek-R1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K34"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:K14"/>
+  <cols>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="64.83203125" customWidth="1"/>
+    <col min="4" max="4" width="60.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="64.83203125" customWidth="1"/>
+    <col min="7" max="7" width="23.83203125" customWidth="1"/>
+    <col min="8" max="8" width="64.83203125" customWidth="1"/>
+    <col min="9" max="9" width="64.83203125" customWidth="1"/>
+    <col min="10" max="10" width="23.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>ID</v>
       </c>
       <c r="B1" t="str">
-        <v>Type</v>
+        <v>Area</v>
       </c>
       <c r="C1" t="str">
-        <v>Builder</v>
+        <v>Scenario</v>
       </c>
       <c r="D1" t="str">
-        <v>Example</v>
+        <v>Risk</v>
       </c>
       <c r="E1" t="str">
-        <v>Purpose</v>
+        <v>Test_Level</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Expected_Result</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Evidence</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Prompt_Source</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Model_Used</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AI-DATA-001</v>
+        <v>FH-MT-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Randomized order</v>
+        <v>Validation</v>
       </c>
       <c r="C2" t="str">
-        <v>createRandomOrder(seed)</v>
+        <v>POST /order with quantity &gt; 20 returns 400</v>
       </c>
       <c r="D2" t="str">
-        <v>Seed 7 creates deterministic mixed menu items</v>
+        <v>Business logic bypass allows invalid quantity</v>
       </c>
       <c r="E2" t="str">
-        <v>Broaden order combinations without shared mutable data</v>
+        <v>Integration</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Response status 400, error 'Invalid order' with details about quantity range</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="H2" t="str">
+        <v>No test exists in tests/integration/api.test.ts for quantity above boundary</v>
+      </c>
+      <c r="I2" t="str">
+        <v>orderService validates quantity between 1 and 20, but no API test for &gt;20</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Code review</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Manual</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AI-DATA-002</v>
+        <v>FH-MT-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Boundary quantity</v>
+        <v>Payment Token</v>
       </c>
       <c r="C3" t="str">
-        <v>createBoundaryQuantityOrder(20)</v>
+        <v>POST /order with unknown gateway token format returns 402</v>
       </c>
       <c r="D3" t="str">
-        <v>burger-classic x 20</v>
+        <v>Payment validation logic may be incomplete</v>
       </c>
       <c r="E3" t="str">
-        <v>Validate upper accepted quantity</v>
+        <v>Integration</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Response status 402, error 'Payment failed' with details 'Payment was not completed through FoodHub Payment Gateway'</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="H3" t="str">
+        <v>No test for token 'gateway_unknown_xxx' or other invalid prefixes; only 'tok_fail' and missing prefix tested</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Test cases: 'gateway_unknown_abc', 'bad_token', empty token (Zod covered)</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Code review</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Manual</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AI-DATA-003</v>
+        <v>FH-MT-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Invalid quantity</v>
+        <v>Validation</v>
       </c>
       <c r="C4" t="str">
-        <v>createBoundaryQuantityOrder(21)</v>
+        <v>POST /order with empty customer name after trimming returns 400</v>
       </c>
       <c r="D4" t="str">
-        <v>burger-classic x 21</v>
+        <v>Incomplete customer data accepted</v>
       </c>
       <c r="E4" t="str">
-        <v>Validate upper rejected quantity</v>
+        <v>Integration</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Response status 400, error 'Invalid order' due to customerName validation failure (Zod .min(1) after trim)</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="H4" t="str">
+        <v>No test with customerName set to whitespace-only string; all integration tests provide a valid name</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Frontend prevents empty name, but API can be called directly</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Code review</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Manual</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AI-DATA-004</v>
+        <v>FH-MT-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Duplicate item lines</v>
+        <v>Persistence</v>
       </c>
       <c r="C5" t="str">
-        <v>createDuplicateItemOrder()</v>
+        <v>OrderRepository.save is called when repository is provided</v>
       </c>
       <c r="D5" t="str">
-        <v>burger-classic x 1 and burger-classic x 2</v>
+        <v>Orders not persisted to database, violating data integrity</v>
       </c>
       <c r="E5" t="str">
-        <v>Validate totals across repeated menu item ids</v>
+        <v>Integration (Testcontainers)</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Saved order receipt matches the created receipt; database contains the order</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Partially Implemented</v>
+      </c>
+      <c r="H5" t="str">
+        <v>README mentions testcontainers integration test exists but no test code visible in current assets</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Missing test code in tests/integration; likely in a separate file not provided</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Requirements document</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Manual</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AI-DATA-005</v>
+        <v>FH-MT-005</v>
       </c>
       <c r="B6" t="str">
-        <v>E2E checkout scenario</v>
+        <v>Error Handling</v>
       </c>
       <c r="C6" t="str">
-        <v>createApprovedCheckout()</v>
+        <v>POST /order when FakePaymentGateway throws an unexpected error (e.g., network timeout)</v>
       </c>
       <c r="D6" t="str">
-        <v>Classic Burger, $9.50, CVV 123</v>
+        <v>Internal server error not properly mapped to 500</v>
       </c>
       <c r="E6" t="str">
-        <v>Keep Playwright happy path data centralized and readable</v>
+        <v>Integration</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Response status 500, error 'Internal server error'</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="H6" t="str">
+        <v>No test simulating payment gateway exception; FakePaymentGateway is synchronous and does not throw</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Would require mocking the payment gateway to throw</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Code review</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Manual</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>AI-DATA-006</v>
+        <v>FH-MT-006</v>
       </c>
       <c r="B7" t="str">
-        <v>E2E declined card</v>
+        <v>Unit</v>
       </c>
       <c r="C7" t="str">
-        <v>createDeclinedPaymentCard()</v>
+        <v>OrderService.createOrder validates items correctly for edge cases (decimal quantity, negative quantity)</v>
       </c>
       <c r="D7" t="str">
-        <v>declined-card with masked number xxxx-xxxx-xxxx-8911</v>
+        <v>Validation bugs missed at unit level</v>
       </c>
       <c r="E7" t="str">
-        <v>Keep payment failure browser data isolated per test</v>
+        <v>Unit</v>
+      </c>
+      <c r="F7" t="str">
+        <v>OrderValidationError is thrown for invalid quantities</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="H7" t="str">
+        <v>No unit tests for OrderService exist; validation only tested via integration tests</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Decimal quantity rejected by Zod positive int, but unit test would catch boundary issues</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Test strategy review</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Manual</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>AI-DATA-007</v>
+        <v>FH-MT-007</v>
       </c>
       <c r="B8" t="str">
-        <v>PostgreSQL persisted order</v>
+        <v>Unit</v>
       </c>
       <c r="C8" t="str">
-        <v>createOrder([{ menuItemId: 'burger-classic', quantity: 2 }])</v>
+        <v>FakePaymentGateway.charge returns appropriate failure reasons for various tokens</v>
       </c>
       <c r="D8" t="str">
-        <v>Saved order total 19 with paymentId pay_testcontainers</v>
+        <v>Payment logic errors not isolated</v>
       </c>
       <c r="E8" t="str">
-        <v>Verify real DB persistence and JSONB item serialization</v>
+        <v>Unit</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Correct PaymentResult for each token category</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="H8" t="str">
+        <v>No unit tests for payment gateway; payment logic is tested only via integration</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Edge cases: empty token, numeric token, special characters</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Code review</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Manual</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>AI-DATA-008</v>
+        <v>FH-MT-008</v>
       </c>
       <c r="B9" t="str">
-        <v>k6 deterministic traffic accounting</v>
+        <v>UI</v>
       </c>
       <c r="C9" t="str">
-        <v>One k6 iteration calls /health, /menu, and /order once</v>
+        <v>Customer cannot proceed with checkout when no items in cart</v>
       </c>
       <c r="D9" t="str">
-        <v>218 iterations = 654 total API requests</v>
+        <v>User may attempt order with empty cart</v>
       </c>
       <c r="E9" t="str">
-        <v>Make load-test evidence easy to audit</v>
+        <v>E2E</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Checkout button is disabled; clicking does not trigger gateway</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Partially Implemented</v>
+      </c>
+      <c r="H9" t="str">
+        <v>E2E test only checks button is disabled when cart is empty (but no explicit test for empty cart checkout attempt)</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Frontend code disables button, but no Playwright test verifies behavior</v>
+      </c>
+      <c r="J9" t="str">
+        <v>UI requirements</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Manual</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>FH-MT-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>UI</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Customer sees error message when returning from gateway without a pending order</v>
+      </c>
+      <c r="D10" t="str">
+        <v>User confused by missing order after payment</v>
+      </c>
+      <c r="E10" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Message shows 'No pending order found after returning from payment.'</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="H10" t="str">
+        <v>No E2E test for this edge case; only happy path tested</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Manually simulated by clearing sessionStorage before redirect</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Code review</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Manual</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>FH-MT-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Consumer contract for GET /menu matches provider specification</v>
+      </c>
+      <c r="D11" t="str">
+        <v>API contract regression between services</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Pact verification passes for menu endpoint</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Partially Implemented</v>
+      </c>
+      <c r="H11" t="str">
+        <v>Pact mentioned in README but no test code provided; likely exists but not shown</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Need to confirm actual pact file and tests</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Requirements document</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Manual</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>FH-MT-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Load</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Order endpoint handles concurrent requests with unique payment tokens</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Race conditions or duplicate payment IDs</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Performance</v>
+      </c>
+      <c r="F12" t="str">
+        <v>All requests succeed (201) with unique paymentId</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Partially Implemented</v>
+      </c>
+      <c r="H12" t="str">
+        <v>k6 test creates orders but uses unique payment tokens per VU/iter; no assertion for uniqueness of paymentId across iterations</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Could add check that each response has a unique paymentId</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Load test analysis</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Manual</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>FH-MT-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Validation</v>
+      </c>
+      <c r="C13" t="str">
+        <v>POST /order with duplicate menuItemId in different quantities adds correctly</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Incorrect total when same item appears multiple times</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Total computed as sum of all lines</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Partially Implemented</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Duplicate item test exists but uses same item twice with same quantity; missing test with different quantities for same item</v>
+      </c>
+      <c r="I13" t="str">
+        <v>createDuplicateItemOrder likely duplicates one item with same quantity; need to test multiple entries of same item with varying quantities</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Code review</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Manual</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>FH-MT-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Observability</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Request logger writes to file when NODE_ENV is not test</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Logging failures silent</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="F14" t="str">
+        <v>File qa-artifacts/observability/raw/request-logs.jsonl contains log entry for the request</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Candidate</v>
+      </c>
+      <c r="H14" t="str">
+        <v>No test for file logging; middleware is skipped in test environment</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Could test with custom environment variable or mock filesystem</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Code review</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Manual</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K14"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:K13"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="64.83203125" customWidth="1"/>
+    <col min="4" max="4" width="64.83203125" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" customWidth="1"/>
+    <col min="6" max="6" width="64.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="64.83203125" customWidth="1"/>
+    <col min="9" max="9" width="64.83203125" customWidth="1"/>
+    <col min="10" max="10" width="45.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Step</v>
+        <v>ID</v>
       </c>
       <c r="B1" t="str">
-        <v>Action</v>
+        <v>Area</v>
       </c>
       <c r="C1" t="str">
-        <v>Detail</v>
+        <v>Scenario</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Risk</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Test_Level</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Expected_Result</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Evidence</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Prompt_Source</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Model_Used</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>CE-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Capture logs</v>
+        <v>Unit</v>
       </c>
       <c r="C2" t="str">
-        <v>Run tests with reporters enabled, then keep Vitest output, Playwright traces, and test-results files</v>
+        <v>OrderService rejects request with zero quantity for a valid menu item</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Validation may allow zero quantity leading to zero line total but still create order</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="F2" t="str">
+        <v>OrderService.createOrder throws OrderValidationError with message 'Quantity must be an integer between 1 and 20'</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Proposed</v>
+      </c>
+      <c r="H2" t="str">
+        <v>tests/unit/orderService.test.ts</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Covers boundary: quantity = 0. OrderFactory can provide such input.</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Manual brainstorming</v>
+      </c>
+      <c r="K2" t="str">
+        <v>None</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>CE-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Run analyzer</v>
+        <v>Unit</v>
       </c>
       <c r="C3" t="str">
-        <v>npm run ai:analyze-failures -- tests/fixtures/failureLogs/sample-flaky-log.txt</v>
+        <v>PaymentService.charge returns failed for amount exactly 0</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Amount 0 could be passed if all items free, leading to unintended free order</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="F3" t="str">
+        <v>FakePaymentGateway.charge(0, 'tok_success') returns { status: 'failed', reason: 'Amount must be greater than zero' }</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Proposed</v>
+      </c>
+      <c r="H3" t="str">
+        <v>tests/unit/paymentService.test.ts</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Edge case: menu items have price &gt;0, but direct gateway call could expose this.</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Manual brainstorming</v>
+      </c>
+      <c r="K3" t="str">
+        <v>None</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>CE-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Feed AI prompt</v>
+        <v>Integration</v>
       </c>
       <c r="C4" t="str">
-        <v>Use qa-artifacts/ai-failure-analysis-prompt.txt with ChatGPT or an internal AI tool</v>
+        <v>POST /order with paymentToken that does not match any known prefix returns 402</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Undocumented token prefix might bypass validation and cause unexpected behavior</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Response status 402 with error 'Payment failed' and details 'Payment was not completed through FoodHub Payment Gateway'</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Proposed</v>
+      </c>
+      <c r="H4" t="str">
+        <v>tests/integration/api.test.ts</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Tokens like 'random_token' should be rejected; currently only specific prefixes accepted.</v>
+      </c>
+      <c r="J4" t="str">
+        <v>AI suggestion from edge case analysis</v>
+      </c>
+      <c r="K4" t="str">
+        <v>DeepSeek</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>CE-004</v>
       </c>
       <c r="B5" t="str">
-        <v>Review output</v>
+        <v>Integration</v>
       </c>
       <c r="C5" t="str">
-        <v>Look for timeout, selector, network, Docker/Testcontainers, Pact verifier, k6 threshold, environment, retry, and ordering patterns</v>
+        <v>POST /order with missing customerName (empty string) returns 400</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Zod schema allows empty string after trim? Actually trim().min(1) prevents empty. But need test.</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Response status 400 with 'Invalid order' and details pointing to 'customerName' field</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Proposed</v>
+      </c>
+      <c r="H5" t="str">
+        <v>tests/integration/api.test.ts</v>
+      </c>
+      <c r="I5" t="str">
+        <v>customerName must be non-empty trimmed string. Test with spaces only.</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Manual brainstorming</v>
+      </c>
+      <c r="K5" t="str">
+        <v>None</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>CE-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Feed current project context</v>
+        <v>Contract</v>
       </c>
       <c r="C6" t="str">
-        <v>Include contract tests, Testcontainers PostgreSQL persistence, k6 load summary, and Playwright E2E artifacts in the AI prompt</v>
+        <v>Pact test for POST /order response when payment fails (402)</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Consumer may expect different error structure than provider returns</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Contract</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Pact interaction validates provider returns correct status and body shape for payment failure</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Proposed</v>
+      </c>
+      <c r="H6" t="str">
+        <v>tests/contract/payment-failure.pact.test.ts</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Currently contract tests may only cover success. Add failure scenario.</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Manual brainstorming</v>
+      </c>
+      <c r="K6" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CE-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Customer uses a custom saved fake card to checkout successfully</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Custom card flow may break after adding new card, affecting user experience</v>
+      </c>
+      <c r="E7" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="F7" t="str">
+        <v>User adds card via form, selects it, completes payment, and sees success message with invoice</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Proposed</v>
+      </c>
+      <c r="H7" t="str">
+        <v>tests/e2e/custom-card-flow.spec.ts</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Covers full cycle: add card -&gt; select -&gt; gateway -&gt; return -&gt; order created.</v>
+      </c>
+      <c r="J7" t="str">
+        <v>AI suggestion from business flow</v>
+      </c>
+      <c r="K7" t="str">
+        <v>DeepSeek</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CE-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Customer sees error message when payment is declined by gateway and returns to app</v>
+      </c>
+      <c r="D8" t="str">
+        <v>User may not see clear error message after redirect, leading to confusion</v>
+      </c>
+      <c r="E8" t="str">
+        <v>E2E</v>
+      </c>
+      <c r="F8" t="str">
+        <v>After declined card and CVV, user is redirected back and sees 'FoodHub Payment Gateway declined this card.' message</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Proposed</v>
+      </c>
+      <c r="H8" t="str">
+        <v>tests/e2e/declined-payment-return.spec.ts</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Current E2E only checks gateway message, not the app's error display after redirect.</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Manual brainstorming</v>
+      </c>
+      <c r="K8" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CE-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Visual</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Visual snapshot of error state when payment fails (after return)</v>
+      </c>
+      <c r="D9" t="str">
+        <v>UI may not render error state correctly across different sizes</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Visual</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Screenshot matches baseline for error message on main page after failed payment</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Proposed</v>
+      </c>
+      <c r="H9" t="str">
+        <v>tests/visual/error-state.spec.ts (Playwright screenshot test)</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Add to visual regression suite. Might need to simulate the session storage.</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Manual brainstorming</v>
+      </c>
+      <c r="K9" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CE-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Load</v>
+      </c>
+      <c r="C10" t="str">
+        <v>k6 test for POST /order with invalid payload ensuring 400 response under load</v>
+      </c>
+      <c r="D10" t="str">
+        <v>High rate of invalid requests may affect error handling performance</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Load</v>
+      </c>
+      <c r="F10" t="str">
+        <v>All 400 responses returned in under 500ms; error rate threshold should not count these as failures</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Proposed</v>
+      </c>
+      <c r="H10" t="str">
+        <v>tests/load/foodhub-api.k6.js (extend with invalid order scenario)</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Add a separate group for validation errors; ensure thresholds exempt 400s from http_req_failed.</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Manual brainstorming</v>
+      </c>
+      <c r="K10" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CE-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Observability</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Unit test for requestLogger middleware creates correct log entry in file</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Observability artifacts may be incomplete or incorrectly formatted, misleading analysis</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Unit</v>
+      </c>
+      <c r="F11" t="str">
+        <v>After a request, the log file contains a valid JSON line with expected fields</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Proposed</v>
+      </c>
+      <c r="H11" t="str">
+        <v>tests/unit/requestLogger.test.ts</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Use temporary directory and mock response. Verify JSON structure.</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Manual brainstorming</v>
+      </c>
+      <c r="K11" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CE-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>CI</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Check that failing E2E tests cause CI pipeline to fail and generate artifacts</v>
+      </c>
+      <c r="D12" t="str">
+        <v>CI may pass despite test failures if not configured correctly</v>
+      </c>
+      <c r="E12" t="str">
+        <v>CI Evidence</v>
+      </c>
+      <c r="F12" t="str">
+        <v>GitHub Actions workflow fails on E2E test failure and attaches playwright report as artifact</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Proposed</v>
+      </c>
+      <c r="H12" t="str">
+        <v>.github/workflows/pr-gate.yml (verify triggers and artifact upload)</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Add a step to force failure simulation; manual check may be sufficient.</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Manual brainstorming</v>
+      </c>
+      <c r="K12" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CE-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Security</v>
+      </c>
+      <c r="C13" t="str">
+        <v>POST /order with XSS payload in customerName is rejected or escaped</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Stored XSS in customerName could affect invoice display or admin panel</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Integration</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Response 201 with customerName stored as-is? Or 400 if schema rejects special chars? At minimum, no script execution.</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Proposed</v>
+      </c>
+      <c r="H13" t="str">
+        <v>tests/integration/security.test.ts</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Current schema allows any string. Consider adding sanitization or acceptance test.</v>
+      </c>
+      <c r="J13" t="str">
+        <v>AI suggestion from failure analysis pattern</v>
+      </c>
+      <c r="K13" t="str">
+        <v>DeepSeek</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K13"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K17"/>
+  <cols>
+    <col min="1" max="1" width="13.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="64.83203125" customWidth="1"/>
+    <col min="4" max="4" width="64.83203125" customWidth="1"/>
+    <col min="5" max="5" width="20.83203125" customWidth="1"/>
+    <col min="6" max="6" width="64.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" customWidth="1"/>
+    <col min="8" max="8" width="64.83203125" customWidth="1"/>
+    <col min="9" max="9" width="64.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Area</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Scenario</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Risk</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Test_Level</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Expected_Result</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Evidence</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Prompt_Source</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Model_Used</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>DATASUG-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>order</v>
+      </c>
+      <c r="C2" t="str">
+        <v>createOrder builder – standard order with multiple valid menu items</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Incorrect total calculation or payment flow for typical orders</v>
+      </c>
+      <c r="E2" t="str">
+        <v>integration</v>
+      </c>
+      <c r="F2" t="str">
+        <v>POST /order returns 201 with correct total, paid status, and item lines</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H2" t="str">
+        <v>tests/fixtures/orderFactory.ts – createOrder() used in api.test.ts</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Provides deterministic baseline for order creation tests</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K2" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DATASUG-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>order</v>
+      </c>
+      <c r="C3" t="str">
+        <v>createBoundaryQuantityOrder – order with maximum quantity (20)</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Quantity boundary validation failure – max 20 per line</v>
+      </c>
+      <c r="E3" t="str">
+        <v>integration</v>
+      </c>
+      <c r="F3" t="str">
+        <v>POST /order returns 201 with total = quantity * unit price</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H3" t="str">
+        <v>tests/fixtures/orderFactory.ts – createBoundaryQuantityOrder(20) used in api.test.ts</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Also test quantity 1 (minimum) and value &gt;20 (rejection)</v>
+      </c>
+      <c r="J3" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K3" t="str">
+        <v>DeepSeek-V3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DATASUG-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>order</v>
+      </c>
+      <c r="C4" t="str">
+        <v>createDuplicateItemOrder – order with repeated menu item lines</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Incorrect total due to duplicate items not being merged</v>
+      </c>
+      <c r="E4" t="str">
+        <v>integration</v>
+      </c>
+      <c r="F4" t="str">
+        <v>POST /order returns 201 with total = sum of duplicate lines (2 × item price)</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H4" t="str">
+        <v>tests/fixtures/orderFactory.ts – createDuplicateItemOrder() used in api.test.ts</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Current behavior allows duplicates; test ensures total is still correct</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K4" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>DATASUG-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>payment</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Valid payment token starting with 'gateway_paid_'</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Payment success flow failure due to token format</v>
+      </c>
+      <c r="E5" t="str">
+        <v>integration</v>
+      </c>
+      <c r="F5" t="str">
+        <v>FakePaymentGateway returns paid status and a paymentId</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H5" t="str">
+        <v>src/services/paymentService.ts – token check for 'gateway_paid_'</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Also test token 'tok_success' as alternative valid token</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K5" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>DATASUG-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>payment</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Declined payment token 'tok_fail'</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Payment failure not properly returned as 402</v>
+      </c>
+      <c r="E6" t="str">
+        <v>integration</v>
+      </c>
+      <c r="F6" t="str">
+        <v>POST /order returns 402 with error 'Payment authorization failed'</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H6" t="str">
+        <v>tests/fixtures/orderFactory.ts – createDeclinedPaymentOrder() uses 'tok_fail'</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Also test token starting with 'gateway_declined_' for same result</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K6" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>DATASUG-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>payment</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Empty or malformed payment token</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Unhandled payment token validation</v>
+      </c>
+      <c r="E7" t="str">
+        <v>integration</v>
+      </c>
+      <c r="F7" t="str">
+        <v>POST /order returns 400 due to Zod schema validation or payment returns failure</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Zod schema requires paymentToken string min 1; payment service checks prefix</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Combine with empty token or token with no valid prefix</v>
+      </c>
+      <c r="J7" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K7" t="str">
+        <v>DeepSeek-V3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>DATASUG-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>customer</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Empty or whitespace-only customer name</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Orders created without a valid customer name</v>
+      </c>
+      <c r="E8" t="str">
+        <v>integration</v>
+      </c>
+      <c r="F8" t="str">
+        <v>POST /order returns 400 – Zod schema requires trimmed name min 1 character</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H8" t="str">
+        <v>app.ts orderSchema: customerName trimmed min 1</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Frontend also validates but API should reject empty names</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K8" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>DATASUG-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>customer</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Customer name with special characters or very long string</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Injection or storage overflow</v>
+      </c>
+      <c r="E9" t="str">
+        <v>unit + integration</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Should pass validation if alphanumeric with spaces; no errors</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H9" t="str">
+        <v>No explicit pattern; test boundary (255 chars)</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Currently no regex; just min length. Consider adding sanitization</v>
+      </c>
+      <c r="J9" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K9" t="str">
+        <v>DeepSeek-V3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>DATASUG-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>invoice</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Invoice data from a successful paid order</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Missing or incorrect invoice fields (orderId, paymentId, customerName, cardLast4)</v>
+      </c>
+      <c r="E10" t="str">
+        <v>e2e</v>
+      </c>
+      <c r="F10" t="str">
+        <v>After successful checkout, invoice link appears and shows correct transactionId, orderId, cardLast4, customerName</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H10" t="str">
+        <v>public/app.js – invoice rendering logic; E2E test order-flow.spec.ts</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Use createApprovedCheckout from e2eData.ts</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K10" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>DATASUG-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>invoice</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Invoice view when no order has been placed</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Invoice preview shown without data or error</v>
+      </c>
+      <c r="E11" t="str">
+        <v>e2e</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Invoice link panel hidden, invoice preview hidden</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H11" t="str">
+        <v>app.js: invoiceLinkPanel.hidden = true initially</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Navigate to / and check that invoice-related elements are not visible</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K11" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>DATASUG-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>observability</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Request log entry for a successful order post</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Log not written or missing fields (timestamp, method, path, status, duration)</v>
+      </c>
+      <c r="E12" t="str">
+        <v>unit / contract</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Log entry appended to request-logs.jsonl with correct fields</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H12" t="str">
+        <v>src/middleware/requestLogger.ts – appends JSONL line</v>
+      </c>
+      <c r="I12" t="str">
+        <v>Simulate with Supertest and check file or mock file system</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K12" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>DATASUG-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>observability</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Log entry for 4xx and 5xx responses</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Error responses not logged or missing duration</v>
+      </c>
+      <c r="E13" t="str">
+        <v>integration</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Log written with correct status code and duration</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H13" t="str">
+        <v>requestLogger logs any status; test with invalid order (400) and payment failure (402)</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Check log contains 'durationMs' &gt; 0</v>
+      </c>
+      <c r="J13" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K13" t="str">
+        <v>DeepSeek-V3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>DATASUG-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>load</v>
+      </c>
+      <c r="C14" t="str">
+        <v>k6 load test with varied order templates (menu items combinations)</v>
+      </c>
+      <c r="D14" t="str">
+        <v>API performance degrades under different payload compositions</v>
+      </c>
+      <c r="E14" t="str">
+        <v>load</v>
+      </c>
+      <c r="F14" t="str">
+        <v>No threshold violations: failure rate &lt;5%, p95 &lt;500ms, order failures &lt;2%</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H14" t="str">
+        <v>tests/load/foodhub-api.k6.js – orderTemplates array and createOrder function</v>
+      </c>
+      <c r="I14" t="str">
+        <v>Run with Docker or local; use npm run test:load</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K14" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>DATASUG-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>load</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Peak load with high number of concurrent users (50 VUs)</v>
+      </c>
+      <c r="D15" t="str">
+        <v>System capacity or connection pool exhaustion</v>
+      </c>
+      <c r="E15" t="str">
+        <v>load</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Thresholds met; no timeout or unhandled errors</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H15" t="str">
+        <v>k6 options support configurable VUs via env VUS</v>
+      </c>
+      <c r="I15" t="str">
+        <v>Run with npm run test:load and BASE_URL=http://127.0.0.1:4173 VUS=50</v>
+      </c>
+      <c r="J15" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K15" t="str">
+        <v>DeepSeek-V3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>DATASUG-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>persistence</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Order saved to PostgreSQL via Testcontainers and retrieved</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Order data not persisted or retrieval fails</v>
+      </c>
+      <c r="E16" t="str">
+        <v>integration</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Order receipt saved and can be read back with same fields</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H16" t="str">
+        <v>orderRepository?.save(receipt) in orderService.ts; testcontainers integration test</v>
+      </c>
+      <c r="I16" t="str">
+        <v>Use real PostgreSQL container; verify save and read</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Manual</v>
+      </c>
+      <c r="K16" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>DATASUG-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>persistence</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Repository save with duplicate orderId</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Primary key violation not handled gracefully</v>
+      </c>
+      <c r="E17" t="str">
+        <v>integration</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Error thrown or idempotent behavior; test defines expected behavior</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Suggested</v>
+      </c>
+      <c r="H17" t="str">
+        <v>orderId is randomUUID – theoretically unique; test duplicate scenario</v>
+      </c>
+      <c r="I17" t="str">
+        <v>Inject repository with duplicate ID; expect appropriate error</v>
+      </c>
+      <c r="J17" t="str">
+        <v>AI-generated</v>
+      </c>
+      <c r="K17" t="str">
+        <v>DeepSeek-V3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K17"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C9"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="2" width="47.83203125" customWidth="1"/>
+    <col min="3" max="3" width="64.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Setting</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Value</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Purpose</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>FOODHUB_AI_LIVE</v>
+      </c>
+      <c r="B2" t="str">
+        <v>true</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Switches real-time DeepSeek API calls on/off</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>DEEPSEEK_API_KEY</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Configured</v>
+      </c>
+      <c r="C3" t="str">
+        <v>DeepSeek bearer token, supplied from local shell or CI/CD secret</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>DEEPSEEK_API_URL</v>
+      </c>
+      <c r="B4" t="str">
+        <v>https://api.deepseek.com/chat/completions</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Optional override for DeepSeek chat completions endpoint</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Failure Analysis Model</v>
+      </c>
+      <c r="B5" t="str">
+        <v>deepseek-v4-pro / thinking enabled / high</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Failure analysis from logs</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Edge Cases Model</v>
+      </c>
+      <c r="B6" t="str">
+        <v>deepseek-v4-flash / thinking enabled / medium</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Test generation from requirements/code</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Missing Scenarios Model</v>
+      </c>
+      <c r="B7" t="str">
+        <v>deepseek-v4-flash / thinking enabled / medium</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Missing test scenarios</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Coverage Expansion Model</v>
+      </c>
+      <c r="B8" t="str">
+        <v>deepseek-v4-flash / thinking enabled / medium</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Coverage expansion</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Test Data Model</v>
+      </c>
+      <c r="B9" t="str">
+        <v>deepseek-v4-flash / thinking enabled / medium</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Test data suggestions</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
   </ignoredErrors>
 </worksheet>
 </file>